--- a/WorkBot/main/data/order_archive/Albert's Organics/Albert's Organics_Bakery_20260509.xlsx
+++ b/WorkBot/main/data/order_archive/Albert's Organics/Albert's Organics_Bakery_20260509.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,132 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>@store</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cost Per</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>@vendor</t>
+          <t>97920</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Albert's Organics</t>
-        </is>
+          <t>Natalie's - Honey Tangerine</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>@date</t>
+          <t>97928</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260509</t>
-        </is>
+          <t>Natalie's - Lemonade</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Cost Per</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Total Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>97920</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Natalie's - Honey Tangerine</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12.16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>97928</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Natalie's - Lemonade</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="E7" t="n">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>97929</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Natalie's - Strawberry Lemonade</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C4" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D4" t="n">
         <v>8.31</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E4" t="n">
         <v>33.24</v>
       </c>
     </row>
